--- a/supporting information/Overview supporting information.xlsx
+++ b/supporting information/Overview supporting information.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>qPCR raw data and per-well efficiencies of the second-step PCR</t>
+          <t>qPCR raw data, per-well efficiencies and melt curves of the second-step PCR</t>
         </is>
       </c>
     </row>
